--- a/zy70942/reconciliation_detailed_BATCH_20260527_001.xlsx
+++ b/zy70942/reconciliation_detailed_BATCH_20260527_001.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-05-27 00:48:52.687623</t>
+          <t>2026-05-27 01:10:48.269473</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27 00:48:52.699522</t>
+          <t>2026-05-27 01:10:48.277057</t>
         </is>
       </c>
     </row>
